--- a/OriginalStudents.xlsx
+++ b/OriginalStudents.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B534DF3E-37CF-4CBA-8594-A3E1C1498441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB5F76A-C8AB-4D1E-A421-12E5E802265B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1392" windowWidth="17664" windowHeight="10848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -213,10 +213,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Pure</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Alexandra</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -305,6 +301,10 @@
   </si>
   <si>
     <t>NaN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Half-Pure</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -699,7 +699,7 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L1" t="s">
         <v>9</v>
@@ -758,7 +758,7 @@
         <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
         <v>19</v>
@@ -807,7 +807,7 @@
         <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
         <v>19</v>
@@ -849,7 +849,7 @@
         <v>28</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
         <v>19</v>
@@ -877,10 +877,10 @@
         <v>947</v>
       </c>
       <c r="E5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" t="s">
         <v>39</v>
-      </c>
-      <c r="F5" t="s">
-        <v>40</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -889,16 +889,16 @@
         <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -915,10 +915,10 @@
         <v>992</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -927,13 +927,13 @@
         <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s">
         <v>18</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O6" s="5" t="str">
         <f>HYPERLINK(5:5,"Alex")</f>
@@ -954,10 +954,10 @@
         <v>992</v>
       </c>
       <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
         <v>48</v>
-      </c>
-      <c r="F7" t="s">
-        <v>49</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -966,16 +966,16 @@
         <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J7" t="s">
         <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O7" s="5" t="str">
         <f>HYPERLINK(5:5,"Alex")</f>
@@ -996,35 +996,35 @@
         <v>994</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8" t="s">
         <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O8" s="5" t="str">
         <f>HYPERLINK(5:5,"Alex")</f>
         <v>Alex</v>
       </c>
       <c r="S8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1035,34 +1035,34 @@
         <v>45492</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
         <v>55</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>56</v>
-      </c>
-      <c r="G9" t="s">
-        <v>57</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" t="s">
         <v>59</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>60</v>
       </c>
-      <c r="K9" t="s">
-        <v>61</v>
-      </c>
       <c r="L9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:19">

--- a/OriginalStudents.xlsx
+++ b/OriginalStudents.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB5F76A-C8AB-4D1E-A421-12E5E802265B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8B6F0B-A244-4BBB-BF7E-1C774F8C3663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1392" windowWidth="17664" windowHeight="10848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="72">
   <si>
     <t>Birthday</t>
     <phoneticPr fontId="1"/>
@@ -49,10 +49,6 @@
   </si>
   <si>
     <t>Sur</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Tribes</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -305,6 +301,50 @@
   </si>
   <si>
     <t>Half-Pure</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gideon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Giesbelt</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ギデオン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ギースベルト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pure</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eustace Thetisius</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fitzarthur</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Merspiegal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Clan</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユースタス・テティシウス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィッツアーサー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -669,16 +709,16 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
         <v>22</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -690,40 +730,40 @@
         <v>3</v>
       </c>
       <c r="H1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>10</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>11</v>
-      </c>
-      <c r="S1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -740,31 +780,31 @@
         <v>975</v>
       </c>
       <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N2" s="5"/>
       <c r="Q2" s="5" t="str">
@@ -772,7 +812,7 @@
         <v>Alex</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -789,28 +829,28 @@
         <v>972</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
         <v>26</v>
       </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>27</v>
       </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M3" s="5" t="str">
         <f>HYPERLINK(2:2,"Galina")</f>
@@ -831,28 +871,28 @@
         <v>992</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
-      </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O4" s="5" t="str">
         <f>HYPERLINK(3:3,"Vermy")</f>
@@ -877,28 +917,28 @@
         <v>947</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
         <v>39</v>
       </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" t="s">
         <v>40</v>
-      </c>
-      <c r="J5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -915,25 +955,25 @@
         <v>992</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
         <v>42</v>
       </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
-      </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O6" s="5" t="str">
         <f>HYPERLINK(5:5,"Alex")</f>
@@ -954,28 +994,28 @@
         <v>992</v>
       </c>
       <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
         <v>47</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
         <v>48</v>
       </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" t="s">
         <v>49</v>
-      </c>
-      <c r="J7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" t="s">
-        <v>50</v>
       </c>
       <c r="O7" s="5" t="str">
         <f>HYPERLINK(5:5,"Alex")</f>
@@ -996,35 +1036,35 @@
         <v>994</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" t="s">
         <v>51</v>
       </c>
-      <c r="G8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" t="s">
         <v>52</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" t="s">
-        <v>53</v>
       </c>
       <c r="O8" s="5" t="str">
         <f>HYPERLINK(5:5,"Alex")</f>
         <v>Alex</v>
       </c>
       <c r="S8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1035,34 +1075,34 @@
         <v>45492</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
         <v>54</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>55</v>
       </c>
-      <c r="G9" t="s">
-        <v>56</v>
-      </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" t="s">
         <v>58</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>59</v>
       </c>
-      <c r="K9" t="s">
-        <v>60</v>
-      </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1079,31 +1119,103 @@
         <v>2023</v>
       </c>
       <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>34</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>35</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>36</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10" t="s">
         <v>37</v>
       </c>
-      <c r="K10" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="3"/>
-      <c r="B11" s="2"/>
+      <c r="A11" s="3">
+        <v>1972</v>
+      </c>
+      <c r="B11" s="2">
+        <v>26630</v>
+      </c>
+      <c r="C11">
+        <v>983</v>
+      </c>
+      <c r="D11">
+        <v>989</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q11" s="5" t="str">
+        <f>HYPERLINK($12:$12,"Thhty")</f>
+        <v>Thhty</v>
+      </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="3"/>
-      <c r="B12" s="2"/>
+      <c r="A12" s="3">
+        <v>1956</v>
+      </c>
+      <c r="B12" s="2">
+        <v>20622</v>
+      </c>
+      <c r="C12">
+        <v>967</v>
+      </c>
+      <c r="D12">
+        <v>973</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="3"/>

--- a/OriginalStudents.xlsx
+++ b/OriginalStudents.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8B6F0B-A244-4BBB-BF7E-1C774F8C3663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BC5B4B-BCA9-4A87-814C-BF0387C51BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5376" yWindow="1296" windowWidth="17664" windowHeight="10848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/OriginalStudents.xlsx
+++ b/OriginalStudents.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BC5B4B-BCA9-4A87-814C-BF0387C51BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C198870-8E69-46A2-8B2A-267CE395C5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5376" yWindow="1296" windowWidth="17664" windowHeight="10848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="91">
   <si>
     <t>Birthday</t>
     <phoneticPr fontId="1"/>
@@ -332,19 +332,94 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>Clan</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユースタス・テティシウス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィッツアーサー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pure</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Richarda=Uliera</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Libau=Kursdolf</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Libau</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arthur=Klaus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>illyrger</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gennad=Jaerius</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>Merspiegal</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Clan</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ユースタス・テティシウス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フィッツアーサー</t>
+    <t>Libau</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Genuina=Lysithea</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wahngrab</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Merspiegal</t>
+  </si>
+  <si>
+    <t>リヒャルダ=ウリエラ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リーバウ=クルスドルフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルトゥール=クラウス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イリュゲル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲナド=イェリオス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メルシュピーガル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲヌイナ=リュシテア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヴァングラッブ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -700,8 +775,9 @@
     <col min="7" max="7" width="22.19921875" customWidth="1"/>
     <col min="8" max="8" width="20.296875" customWidth="1"/>
     <col min="9" max="9" width="25.09765625" customWidth="1"/>
-    <col min="10" max="10" width="9.8984375" customWidth="1"/>
+    <col min="10" max="10" width="31.19921875" customWidth="1"/>
     <col min="11" max="11" width="9.796875" customWidth="1"/>
+    <col min="12" max="12" width="10.69921875" customWidth="1"/>
     <col min="16" max="16" width="9.19921875" customWidth="1"/>
     <col min="18" max="18" width="9.69921875" customWidth="1"/>
     <col min="19" max="19" width="12.69921875" customWidth="1"/>
@@ -730,7 +806,7 @@
         <v>3</v>
       </c>
       <c r="H1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I1" t="s">
         <v>4</v>
@@ -1202,13 +1278,13 @@
         <v>67</v>
       </c>
       <c r="H12" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12" t="s">
         <v>70</v>
-      </c>
-      <c r="J12" t="s">
-        <v>71</v>
       </c>
       <c r="K12" t="s">
         <v>44</v>
@@ -1218,20 +1294,102 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="3"/>
-      <c r="B13" s="2"/>
+      <c r="A13" s="3">
+        <v>1934</v>
+      </c>
+      <c r="B13" s="2">
+        <v>12691</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="3"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="3">
+        <v>1933</v>
+      </c>
+      <c r="B14" s="2">
+        <v>12236</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="3"/>
-      <c r="B15" s="2"/>
+      <c r="A15" s="3">
+        <v>1931</v>
+      </c>
+      <c r="B15" s="2">
+        <v>11354</v>
+      </c>
+      <c r="E15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="3"/>
-      <c r="B16" s="2"/>
+      <c r="A16" s="3">
+        <v>1936</v>
+      </c>
+      <c r="B16" s="2">
+        <v>13212</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3"/>

--- a/OriginalStudents.xlsx
+++ b/OriginalStudents.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C198870-8E69-46A2-8B2A-267CE395C5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7AD51A-B7C2-45FD-9644-CD9670CA4ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="99">
   <si>
     <t>Birthday</t>
     <phoneticPr fontId="1"/>
@@ -71,10 +71,6 @@
   </si>
   <si>
     <t>ParentA2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Domitory</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -217,10 +213,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Hufflepuff</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Frances</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -296,10 +288,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NaN</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Half-Pure</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -348,10 +336,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Richarda=Uliera</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Libau=Kursdolf</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -368,10 +352,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Gennad=Jaerius</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Merspiegal</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -380,10 +360,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Genuina=Lysithea</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Wahngrab</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -420,6 +396,62 @@
   </si>
   <si>
     <t>ヴァングラッブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Barnaba Ramiela</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Richarda Uliera</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gennad Jaerius</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Genuina Lysithea</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Libau=Kursdolf</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Libau</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hettia Cassiela</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gryffindor</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hufflepuff</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ilvermorny</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wampus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>House</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バーナバ・ラミエラ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘティア・キャシエラ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -785,16 +817,16 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
         <v>21</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -806,7 +838,7 @@
         <v>3</v>
       </c>
       <c r="H1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I1" t="s">
         <v>4</v>
@@ -815,16 +847,16 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L1" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="M1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" t="s">
         <v>19</v>
-      </c>
-      <c r="N1" t="s">
-        <v>20</v>
       </c>
       <c r="O1" t="s">
         <v>6</v>
@@ -833,13 +865,13 @@
         <v>7</v>
       </c>
       <c r="Q1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>10</v>
-      </c>
-      <c r="S1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -850,37 +882,37 @@
         <v>21271</v>
       </c>
       <c r="C2" s="4">
-        <v>969</v>
+        <v>1969</v>
       </c>
       <c r="D2">
-        <v>975</v>
+        <v>1975</v>
       </c>
       <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N2" s="5"/>
       <c r="Q2" s="5" t="str">
@@ -888,7 +920,7 @@
         <v>Alex</v>
       </c>
       <c r="S2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -899,34 +931,34 @@
         <v>45469</v>
       </c>
       <c r="C3">
-        <v>966</v>
+        <v>1966</v>
       </c>
       <c r="D3">
-        <v>972</v>
+        <v>1972</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
       <c r="K3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M3" s="5" t="str">
         <f>HYPERLINK(2:2,"Galina")</f>
@@ -941,34 +973,34 @@
         <v>27736</v>
       </c>
       <c r="C4">
-        <v>987</v>
+        <v>1987</v>
       </c>
       <c r="D4">
-        <v>992</v>
+        <v>1992</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
       <c r="J4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O4" s="5" t="str">
         <f>HYPERLINK(3:3,"Vermy")</f>
@@ -987,34 +1019,34 @@
         <v>14278</v>
       </c>
       <c r="C5">
-        <v>941</v>
+        <v>1941</v>
       </c>
       <c r="D5">
-        <v>947</v>
+        <v>1947</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="s">
         <v>38</v>
       </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" t="s">
-        <v>39</v>
-      </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="L5" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1025,31 +1057,31 @@
         <v>26949</v>
       </c>
       <c r="C6">
-        <v>984</v>
+        <v>1984</v>
       </c>
       <c r="D6">
-        <v>992</v>
+        <v>1992</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O6" s="5" t="str">
         <f>HYPERLINK(5:5,"Alex")</f>
@@ -1064,34 +1096,34 @@
         <v>27658</v>
       </c>
       <c r="C7">
-        <v>987</v>
+        <v>1987</v>
       </c>
       <c r="D7">
-        <v>992</v>
+        <v>1992</v>
       </c>
       <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
         <v>46</v>
       </c>
-      <c r="F7" t="s">
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" t="s">
         <v>47</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" t="s">
-        <v>49</v>
       </c>
       <c r="O7" s="5" t="str">
         <f>HYPERLINK(5:5,"Alex")</f>
@@ -1106,41 +1138,41 @@
         <v>28198</v>
       </c>
       <c r="C8">
-        <v>988</v>
+        <v>1988</v>
       </c>
       <c r="D8">
-        <v>994</v>
+        <v>1994</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" t="s">
         <v>50</v>
-      </c>
-      <c r="G8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" t="s">
-        <v>52</v>
       </c>
       <c r="O8" s="5" t="str">
         <f>HYPERLINK(5:5,"Alex")</f>
         <v>Alex</v>
       </c>
       <c r="S8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1150,35 +1182,23 @@
       <c r="B9" s="2">
         <v>45492</v>
       </c>
-      <c r="C9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
       <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" t="s">
         <v>53</v>
       </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s">
         <v>55</v>
       </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="s">
-        <v>57</v>
-      </c>
       <c r="J9" t="s">
-        <v>58</v>
-      </c>
-      <c r="K9" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1195,25 +1215,25 @@
         <v>2023</v>
       </c>
       <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>33</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>34</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>35</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" t="s">
         <v>36</v>
-      </c>
-      <c r="K10" t="s">
-        <v>44</v>
-      </c>
-      <c r="L10" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1224,31 +1244,31 @@
         <v>26630</v>
       </c>
       <c r="C11">
-        <v>983</v>
+        <v>1983</v>
       </c>
       <c r="D11">
-        <v>989</v>
+        <v>1989</v>
       </c>
       <c r="E11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" t="s">
         <v>60</v>
       </c>
-      <c r="F11" t="s">
+      <c r="J11" t="s">
         <v>61</v>
       </c>
-      <c r="G11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J11" t="s">
-        <v>64</v>
-      </c>
       <c r="K11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q11" s="5" t="str">
         <f>HYPERLINK($12:$12,"Thhty")</f>
@@ -1263,34 +1283,34 @@
         <v>20622</v>
       </c>
       <c r="C12">
-        <v>967</v>
+        <v>1967</v>
       </c>
       <c r="D12">
-        <v>973</v>
+        <v>1973</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s">
         <v>66</v>
       </c>
-      <c r="G12" t="s">
+      <c r="J12" t="s">
         <v>67</v>
       </c>
-      <c r="H12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I12" t="s">
-        <v>69</v>
-      </c>
-      <c r="J12" t="s">
-        <v>70</v>
-      </c>
       <c r="K12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1300,23 +1320,35 @@
       <c r="B13" s="2">
         <v>12691</v>
       </c>
+      <c r="C13">
+        <v>1946</v>
+      </c>
+      <c r="D13">
+        <v>1952</v>
+      </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I13" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+      <c r="K13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1326,20 +1358,32 @@
       <c r="B14" s="2">
         <v>12236</v>
       </c>
+      <c r="C14">
+        <v>1944</v>
+      </c>
+      <c r="D14">
+        <v>1950</v>
+      </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="J14" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="K14" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1350,22 +1394,22 @@
         <v>11354</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" t="s">
         <v>82</v>
-      </c>
-      <c r="I15" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1375,83 +1419,154 @@
       <c r="B16" s="2">
         <v>13212</v>
       </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I16" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="3">
+        <v>1958</v>
+      </c>
+      <c r="B17" s="2">
+        <v>21205</v>
+      </c>
+      <c r="C17">
+        <v>1969</v>
+      </c>
+      <c r="D17">
+        <v>1976</v>
+      </c>
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" t="s">
         <v>89</v>
       </c>
-      <c r="J16" t="s">
+      <c r="H17" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="I17" t="s">
+        <v>97</v>
+      </c>
+      <c r="J17" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" t="s">
+        <v>42</v>
+      </c>
+      <c r="L17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="3">
+        <v>1967</v>
+      </c>
+      <c r="B18" s="2">
+        <v>45888</v>
+      </c>
+      <c r="C18">
+        <v>1979</v>
+      </c>
+      <c r="D18">
+        <v>1985</v>
+      </c>
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" t="s">
+        <v>42</v>
+      </c>
+      <c r="L18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="3"/>
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:12">
       <c r="A20" s="3"/>
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:12">
       <c r="A21" s="3"/>
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:12">
       <c r="A22" s="3"/>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:12">
       <c r="A23" s="3"/>
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:12">
       <c r="A24" s="3"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:12">
       <c r="A25" s="3"/>
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:12">
       <c r="A26" s="3"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:12">
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:12">
       <c r="A28" s="3"/>
       <c r="B28" s="2"/>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:12">
       <c r="A29" s="3"/>
       <c r="B29" s="2"/>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:12">
       <c r="A30" s="3"/>
       <c r="B30" s="2"/>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:12">
       <c r="A31" s="3"/>
       <c r="B31" s="2"/>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:12">
       <c r="A32" s="3"/>
       <c r="B32" s="2"/>
     </row>

--- a/OriginalStudents.xlsx
+++ b/OriginalStudents.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7AD51A-B7C2-45FD-9644-CD9670CA4ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180FDA01-35C1-4B77-B344-E657354BF2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -928,7 +928,7 @@
         <v>1955</v>
       </c>
       <c r="B3" s="2">
-        <v>45469</v>
+        <v>20266</v>
       </c>
       <c r="C3">
         <v>1966</v>

--- a/OriginalStudents.xlsx
+++ b/OriginalStudents.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180FDA01-35C1-4B77-B344-E657354BF2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C17C0B-D1B4-459B-914D-5D92A8A85A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9624" yWindow="720" windowWidth="13416" windowHeight="10848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
